--- a/WebDataBase/LabDatabase/static/LabDatabase/DownloadFile/PartColumn.xlsx
+++ b/WebDataBase/LabDatabase/static/LabDatabase/DownloadFile/PartColumn.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\WebDatabase\WebDataWorld\LabDatabase\static\LabDatabase\DownloadFile\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{265EBB0D-4163-4B82-8D62-EC7D1942730C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54DEF990-B1D6-4363-BC11-159B87BC3B67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9330" yWindow="6225" windowWidth="19695" windowHeight="11340" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Part" sheetId="3" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t>Alias</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -48,6 +48,60 @@
   </si>
   <si>
     <t>Note</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在此填写标准名称，限20字符以内</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>别称，可以识别当前元件内容的名称</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>元件种类，在promoter，rbs，cds，terminator，p+r中挑选一个填入</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>序列信息</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>物种信息</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>备注信息</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>必填项</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PRO910</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>HXT1</t>
+  </si>
+  <si>
+    <t>promoter</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GCCACAATGAAACTTCAATTCATATCGACCGACTATTTTTCTCCGAACCAAAAAAATAGCAGGGCGAGATTGGAGCTGCGGAAAAAAGAGGAAAAAATTTTTTCGTAGTTTTCTTGTGCAAATTAGGGTGTAAGGTTTCTAGGGCTTATTGGTTCAAGCAGAAGAGACAACAATTGTAGGTCCTAAATTCAAGGCGGATGTAAGGAGTATTGGTTTCGAAAGTTTTTCCGAAGCGGCATGGCAGGGACTACTTGCGCATGCGCTCGGATTATCTTCATTTTTGCTTGCAAAAACGTAGAATCATGGTAAATTACATGAAGAATTCTCTTTTTTTTTTTTTTTTTTTTTTTTTTACCTCTAAAGAGTGTTGACCAACTGAAAAAACCCTTCTTCAAGAGAGTTAAACTAAGACTAACCATCATAACTTCCAAGGAATTAATCGATATCTTGCACTCCTGATTTTTCTTCAAAGAGACAGCGCAAAGGATTATGACACTGTTGCATTGAGTCAAAAGTTTTTCCGAAGTGACCCAGTGCTCTTTTTTTTTTTCCGTGAAGGACTGACAAATATGCGCACAAGATCCAATACGTAATGGAAATTCGGAAAAACTAGGAAGAAATGCTGCAGGGCATTGCCGTGCCGATCTTTTGTCTTTCAGATATATGAGAAAAAGAATATTCATCAAGTGCTGATAGAAGAATACCACTCATATGACGTGGGCAGAGGACAGCAAACGTAAACATGAGCTGCTGCGACATTTGATGGCTTTTATCCGACAAGCCAGGAAACTCCACCATTATCTAATGTAGCAAAATATTTCTTAACACCCGAAGTTGCGTGTCCCCCTCACGTTTTTAATCATTTGAATTAGTATATTGAAATTATATATAAAGGCAACAATGTCCCCATAATCAATTCCATCTGGGGACTCATGTTCTTTCCCCACCTTAAAATCTATAAAGATATCATAATCGTCAACTAGTTGATATACGTAAAATC</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Saccharomyces cerevisiae</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>From CDN design 1000bp</t>
+  </si>
+  <si>
+    <t>开始上传时，请务必确认删除2-4行</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -71,12 +125,24 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -91,8 +157,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -373,15 +443,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC7B2FE6-83CF-4953-BC21-50CF73AE0A95}">
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="13.25" customWidth="1"/>
-    <col min="2" max="3" width="10.625" customWidth="1"/>
-    <col min="4" max="4" width="11.5" customWidth="1"/>
+    <col min="1" max="1" width="47.5" customWidth="1"/>
+    <col min="2" max="2" width="38.875" customWidth="1"/>
+    <col min="3" max="3" width="61.125" customWidth="1"/>
+    <col min="4" max="4" width="13.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>4</v>
       </c>
@@ -401,7 +472,64 @@
         <v>5</v>
       </c>
     </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A4" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+    </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A4:G4"/>
+  </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
